--- a/Config/Excel/CardConfig.xlsx
+++ b/Config/Excel/CardConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="211">
   <si>
     <t>Id</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
   </si>
   <si>
     <t>SingleGrab</t>
@@ -87,6 +93,12 @@
   </si>
   <si>
     <t>价值</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <r>
@@ -613,6 +625,9 @@
     <t>cardHeartsSpider</t>
   </si>
   <si>
+    <t>可以连接任意红心牌，作为任意点数使用</t>
+  </si>
+  <si>
     <t>0200002</t>
   </si>
   <si>
@@ -622,6 +637,9 @@
     <t>cardClubsSpider</t>
   </si>
   <si>
+    <t>可以连接任意梅花牌，作为任意点数使用</t>
+  </si>
+  <si>
     <t>0200003</t>
   </si>
   <si>
@@ -631,6 +649,9 @@
     <t>cardSpadesSpider</t>
   </si>
   <si>
+    <t>可以连接任意黑桃牌，作为任意点数使用</t>
+  </si>
+  <si>
     <t>0200004</t>
   </si>
   <si>
@@ -640,6 +661,9 @@
     <t>cardDiamondsSpider</t>
   </si>
   <si>
+    <t>可以连接任意方块牌，作为任意点数使用</t>
+  </si>
+  <si>
     <t>0300001</t>
   </si>
   <si>
@@ -649,6 +673,9 @@
     <t>cardBlack</t>
   </si>
   <si>
+    <t>不可以和任意牌连接</t>
+  </si>
+  <si>
     <t>0200005</t>
   </si>
   <si>
@@ -658,6 +685,9 @@
     <t>cardSpider</t>
   </si>
   <si>
+    <t>可以连接任意点数花色牌，作为任意点数花色使用</t>
+  </si>
+  <si>
     <t>0200006</t>
   </si>
   <si>
@@ -667,6 +697,9 @@
     <t>cardCopy</t>
   </si>
   <si>
+    <t>移动到任意牌上，将自己变成那张牌</t>
+  </si>
+  <si>
     <t>0200007</t>
   </si>
   <si>
@@ -674,6 +707,9 @@
   </si>
   <si>
     <t>cardRecycle</t>
+  </si>
+  <si>
+    <t>移动到任意牌上，将自己和那张牌放入弃牌堆</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1890,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:K63"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
@@ -1863,12 +1899,14 @@
     <col min="4" max="4" width="22.0277777777778" customWidth="1"/>
     <col min="5" max="5" width="26.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="23.3796296296296" customWidth="1"/>
-    <col min="7" max="7" width="24.2407407407407" customWidth="1"/>
-    <col min="8" max="8" width="22.7037037037037" customWidth="1"/>
-    <col min="9" max="9" width="17.1018518518519" customWidth="1"/>
+    <col min="7" max="7" width="19.3240740740741" customWidth="1"/>
+    <col min="8" max="8" width="21.3518518518519" customWidth="1"/>
+    <col min="9" max="9" width="26.962962962963" customWidth="1"/>
+    <col min="10" max="10" width="22.7037037037037" customWidth="1"/>
+    <col min="11" max="11" width="17.1018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1894,23 +1932,29 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -1919,45 +1963,57 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" ht="43.2" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="43.2" spans="1:11">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
+      <c r="G3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D4" s="5">
         <v>0</v>
@@ -1968,25 +2024,28 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="H4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -1997,25 +2056,28 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" s="5">
         <v>0</v>
@@ -2026,25 +2088,28 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="H6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -2055,25 +2120,28 @@
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="H7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" s="5">
         <v>0</v>
@@ -2084,25 +2152,28 @@
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D9" s="5">
         <v>0</v>
@@ -2113,25 +2184,28 @@
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="H9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D10" s="5">
         <v>0</v>
@@ -2142,25 +2216,28 @@
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="H10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D11" s="5">
         <v>0</v>
@@ -2171,25 +2248,28 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="H11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D12" s="5">
         <v>0</v>
@@ -2200,25 +2280,28 @@
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="H12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5">
         <v>0</v>
@@ -2229,25 +2312,28 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5">
         <v>0</v>
@@ -2258,25 +2344,28 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="H14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D15" s="5">
         <v>0</v>
@@ -2287,25 +2376,28 @@
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="H15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D16" s="5">
         <v>0</v>
@@ -2316,25 +2408,28 @@
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="H16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D17" s="5">
         <v>1</v>
@@ -2345,25 +2440,28 @@
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="H17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="5">
         <v>1</v>
@@ -2374,25 +2472,28 @@
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="H18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D19" s="5">
         <v>1</v>
@@ -2403,25 +2504,28 @@
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="H19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D20" s="5">
         <v>1</v>
@@ -2432,25 +2536,28 @@
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="H20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="6" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D21" s="5">
         <v>1</v>
@@ -2461,25 +2568,28 @@
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="H21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D22" s="5">
         <v>1</v>
@@ -2490,25 +2600,28 @@
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="H22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D23" s="5">
         <v>1</v>
@@ -2519,25 +2632,28 @@
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" t="b">
-        <v>0</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="H23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D24" s="5">
         <v>1</v>
@@ -2548,25 +2664,28 @@
       <c r="F24">
         <v>0</v>
       </c>
-      <c r="G24" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="H24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D25" s="5">
         <v>1</v>
@@ -2577,25 +2696,28 @@
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="H25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="6" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D26" s="5">
         <v>1</v>
@@ -2606,25 +2728,28 @@
       <c r="F26">
         <v>0</v>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="H26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D27" s="5">
         <v>1</v>
@@ -2635,25 +2760,28 @@
       <c r="F27">
         <v>0</v>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="H27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D28" s="5">
         <v>1</v>
@@ -2664,25 +2792,28 @@
       <c r="F28">
         <v>0</v>
       </c>
-      <c r="G28" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="H28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D29" s="5">
         <v>1</v>
@@ -2693,25 +2824,28 @@
       <c r="F29">
         <v>0</v>
       </c>
-      <c r="G29" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="H29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="6" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D30" s="5">
         <v>2</v>
@@ -2722,25 +2856,28 @@
       <c r="F30">
         <v>0</v>
       </c>
-      <c r="G30" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="H30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="6" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D31" s="5">
         <v>2</v>
@@ -2751,25 +2888,28 @@
       <c r="F31">
         <v>0</v>
       </c>
-      <c r="G31" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="H31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" s="5">
         <v>2</v>
@@ -2780,25 +2920,28 @@
       <c r="F32">
         <v>0</v>
       </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+      <c r="H32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D33" s="5">
         <v>2</v>
@@ -2809,25 +2952,28 @@
       <c r="F33">
         <v>0</v>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+      <c r="H33" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D34" s="5">
         <v>2</v>
@@ -2838,25 +2984,28 @@
       <c r="F34">
         <v>0</v>
       </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+      <c r="H34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D35" s="5">
         <v>2</v>
@@ -2867,25 +3016,28 @@
       <c r="F35">
         <v>0</v>
       </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+      <c r="H35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D36" s="5">
         <v>2</v>
@@ -2896,25 +3048,28 @@
       <c r="F36">
         <v>0</v>
       </c>
-      <c r="G36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+      <c r="H36" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C37" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D37" s="5">
         <v>2</v>
@@ -2925,25 +3080,28 @@
       <c r="F37">
         <v>0</v>
       </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+      <c r="H37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D38" s="5">
         <v>2</v>
@@ -2954,25 +3112,28 @@
       <c r="F38">
         <v>0</v>
       </c>
-      <c r="G38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+      <c r="H38" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" s="6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D39" s="5">
         <v>2</v>
@@ -2983,25 +3144,28 @@
       <c r="F39">
         <v>0</v>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+      <c r="H39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D40" s="5">
         <v>2</v>
@@ -3012,25 +3176,28 @@
       <c r="F40">
         <v>0</v>
       </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="H40" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D41" s="5">
         <v>2</v>
@@ -3041,25 +3208,28 @@
       <c r="F41">
         <v>0</v>
       </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+      <c r="H41" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" s="6" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D42" s="5">
         <v>2</v>
@@ -3070,25 +3240,28 @@
       <c r="F42">
         <v>0</v>
       </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="H42" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C43" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D43" s="5">
         <v>3</v>
@@ -3099,25 +3272,28 @@
       <c r="F43">
         <v>0</v>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+      <c r="H43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" s="6" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D44" s="5">
         <v>3</v>
@@ -3128,25 +3304,28 @@
       <c r="F44">
         <v>0</v>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+      <c r="H44" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" s="6" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C45" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D45" s="5">
         <v>3</v>
@@ -3157,25 +3336,28 @@
       <c r="F45">
         <v>0</v>
       </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+      <c r="H45" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D46" s="5">
         <v>3</v>
@@ -3186,25 +3368,28 @@
       <c r="F46">
         <v>0</v>
       </c>
-      <c r="G46" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+      <c r="H46" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D47" s="5">
         <v>3</v>
@@ -3215,25 +3400,28 @@
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="G47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+      <c r="H47" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D48" s="5">
         <v>3</v>
@@ -3244,25 +3432,28 @@
       <c r="F48">
         <v>0</v>
       </c>
-      <c r="G48" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+      <c r="H48" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D49" s="5">
         <v>3</v>
@@ -3273,25 +3464,28 @@
       <c r="F49">
         <v>0</v>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+      <c r="H49" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
       <c r="A50" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D50" s="5">
         <v>3</v>
@@ -3302,25 +3496,28 @@
       <c r="F50">
         <v>0</v>
       </c>
-      <c r="G50" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+      <c r="H50" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D51" s="5">
         <v>3</v>
@@ -3331,25 +3528,28 @@
       <c r="F51">
         <v>0</v>
       </c>
-      <c r="G51" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
+      <c r="H51" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" s="6" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D52" s="5">
         <v>3</v>
@@ -3360,25 +3560,28 @@
       <c r="F52">
         <v>0</v>
       </c>
-      <c r="G52" t="b">
-        <v>0</v>
-      </c>
-      <c r="H52" t="b">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
+      <c r="H52" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C53" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D53" s="5">
         <v>3</v>
@@ -3389,25 +3592,28 @@
       <c r="F53">
         <v>0</v>
       </c>
-      <c r="G53" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
+      <c r="H53" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" s="6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D54" s="5">
         <v>3</v>
@@ -3418,25 +3624,28 @@
       <c r="F54">
         <v>0</v>
       </c>
-      <c r="G54" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
+      <c r="H54" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" s="6" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D55" s="5">
         <v>3</v>
@@ -3447,25 +3656,28 @@
       <c r="F55">
         <v>0</v>
       </c>
-      <c r="G55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
+      <c r="H55" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -3476,25 +3688,31 @@
       <c r="F56">
         <v>150</v>
       </c>
-      <c r="G56" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="G56" t="s">
+        <v>180</v>
+      </c>
+      <c r="H56" t="s">
+        <v>182</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -3505,25 +3723,31 @@
       <c r="F57">
         <v>150</v>
       </c>
-      <c r="G57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
+      <c r="G57" t="s">
+        <v>184</v>
+      </c>
+      <c r="H57" t="s">
+        <v>186</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="7" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C58" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -3534,25 +3758,31 @@
       <c r="F58">
         <v>150</v>
       </c>
-      <c r="G58" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
+      <c r="G58" t="s">
+        <v>188</v>
+      </c>
+      <c r="H58" t="s">
+        <v>190</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" s="7" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D59">
         <v>3</v>
@@ -3563,25 +3793,31 @@
       <c r="F59">
         <v>150</v>
       </c>
-      <c r="G59" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
+      <c r="G59" t="s">
+        <v>192</v>
+      </c>
+      <c r="H59" t="s">
+        <v>194</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="7" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C60" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D60">
         <v>-2</v>
@@ -3592,25 +3828,31 @@
       <c r="F60">
         <v>-70</v>
       </c>
-      <c r="G60" t="b">
+      <c r="G60" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" t="s">
+        <v>198</v>
+      </c>
+      <c r="I60" t="b">
         <v>1</v>
       </c>
-      <c r="H60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" s="7" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="D61">
         <v>-1</v>
@@ -3621,25 +3863,31 @@
       <c r="F61">
         <v>350</v>
       </c>
-      <c r="G61" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" t="b">
+      <c r="G61" t="s">
+        <v>200</v>
+      </c>
+      <c r="H61" t="s">
+        <v>202</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
         <v>1</v>
       </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
+      <c r="K61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" s="7" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="B62" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C62" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D62">
         <v>-2</v>
@@ -3650,25 +3898,31 @@
       <c r="F62">
         <v>150</v>
       </c>
-      <c r="G62" t="b">
+      <c r="G62" t="s">
+        <v>204</v>
+      </c>
+      <c r="H62" t="s">
+        <v>206</v>
+      </c>
+      <c r="I62" t="b">
         <v>1</v>
       </c>
-      <c r="H62" t="b">
+      <c r="J62" t="b">
         <v>1</v>
       </c>
-      <c r="I62">
+      <c r="K62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:11">
       <c r="A63" s="7" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C63" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="D63">
         <v>-2</v>
@@ -3679,13 +3933,19 @@
       <c r="F63">
         <v>80</v>
       </c>
-      <c r="G63" t="b">
+      <c r="G63" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" t="s">
+        <v>210</v>
+      </c>
+      <c r="I63" t="b">
         <v>1</v>
       </c>
-      <c r="H63" t="b">
+      <c r="J63" t="b">
         <v>1</v>
       </c>
-      <c r="I63">
+      <c r="K63">
         <v>1</v>
       </c>
     </row>

--- a/Config/Excel/CardConfig.xlsx
+++ b/Config/Excel/CardConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Price</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>PlaceSkill</t>
   </si>
   <si>
@@ -70,12 +64,6 @@
     <t>价值</t>
   </si>
   <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
     <t>放下后技能</t>
   </si>
   <si>
@@ -88,9 +76,6 @@
     <t>cardBlack</t>
   </si>
   <si>
-    <t>不可以和任意牌连接</t>
-  </si>
-  <si>
     <t>S_m_0200001</t>
   </si>
   <si>
@@ -100,9 +85,6 @@
     <t>cardCopy</t>
   </si>
   <si>
-    <t>移动到任意牌上，将自己变成那张牌</t>
-  </si>
-  <si>
     <t>S_m_0200002</t>
   </si>
   <si>
@@ -110,9 +92,6 @@
   </si>
   <si>
     <t>cardRecycle</t>
-  </si>
-  <si>
-    <t>移动到任意牌上，将自己和那张牌放入弃牌堆</t>
   </si>
 </sst>
 </file>
@@ -1271,19 +1250,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="15.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
     <col min="3" max="3" width="29.2685185185185" customWidth="1"/>
     <col min="4" max="4" width="19.037037037037" customWidth="1"/>
-    <col min="5" max="5" width="19.3240740740741" customWidth="1"/>
-    <col min="6" max="6" width="27.5277777777778" customWidth="1"/>
-    <col min="7" max="7" width="17.1018518518519" customWidth="1"/>
+    <col min="5" max="5" width="17.1018518518519" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1297,121 +1274,85 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:5">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
         <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
       </c>
       <c r="D4">
         <v>-70</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
         <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
       </c>
       <c r="D5">
         <v>150</v>
       </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5">
+      <c r="E5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>80</v>
       </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6">
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
